--- a/apps_nicolo/LogicCircuits_4s_6r_HF_REINFORCE_nonzeroic/LogicCircuits_4s_6r_HF_REINFORCE_SIL_nonzeroic.xlsx
+++ b/apps_nicolo/LogicCircuits_4s_6r_HF_REINFORCE_nonzeroic/LogicCircuits_4s_6r_HF_REINFORCE_SIL_nonzeroic.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1105,8 +1105,184 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-04 16:17:32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/logiccircuits-4s-6r-hf-reinforce-sil-nonzeroic/a589d7a7d1444a3ca5a632d6a3a70c46</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>(6, 4, 3, 1280)</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M8" t="n">
+        <v>128</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>{'structure': 3.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.33676424447995346), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-04 17:37:29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/logiccircuits-4s-6r-hf-reinforce-sil-nonzeroic/a1d281ee57c8434ebd47b4990953b044</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>(6, 9, 8, 1280)</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M9" t="n">
+        <v>128</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>256</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>{'structure': 3.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.22057932482003562), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z7"/>
+  <autoFilter ref="A1:Z9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>